--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\DEV\Report-Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F487A2-F5C0-45A8-B383-544BED923297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C657074-2F25-4E84-979E-5CF09CF8CADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="mappings" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\DEV\Report-Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C657074-2F25-4E84-979E-5CF09CF8CADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1528630C-984D-4333-8943-B9A494206054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
   <si>
     <t>Spreadsheet Column</t>
   </si>
@@ -262,9 +262,6 @@
   </si>
   <si>
     <t>(computed) numero_rapport</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>Generated filename component/counter</t>
@@ -648,10 +645,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -902,7 +899,7 @@
         <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
         <v>53</v>
@@ -930,7 +927,7 @@
         <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
         <v>53</v>
@@ -955,10 +952,10 @@
         <v>61</v>
       </c>
       <c r="C27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" t="s">
         <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
       </c>
       <c r="E27" t="s">
         <v>62</v>
@@ -972,10 +969,10 @@
         <v>64</v>
       </c>
       <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" t="s">
         <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>86</v>
       </c>
       <c r="E28" t="s">
         <v>65</v>
@@ -1025,10 +1022,10 @@
         <v>75</v>
       </c>
       <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" t="s">
         <v>87</v>
-      </c>
-      <c r="D32" t="s">
-        <v>88</v>
       </c>
       <c r="E32" t="s">
         <v>76</v>
@@ -1038,37 +1035,32 @@
       <c r="A33" t="s">
         <v>77</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
         <v>78</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>